--- a/data/nzd0553/nzd0553.xlsx
+++ b/data/nzd0553/nzd0553.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K509"/>
+  <dimension ref="A1:K510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20295,6 +20295,45 @@
       <c r="K509" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:27:15+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>308.46</v>
+      </c>
+      <c r="C510" t="n">
+        <v>312.57</v>
+      </c>
+      <c r="D510" t="n">
+        <v>324.36</v>
+      </c>
+      <c r="E510" t="n">
+        <v>322.81</v>
+      </c>
+      <c r="F510" t="n">
+        <v>320.61</v>
+      </c>
+      <c r="G510" t="n">
+        <v>330.07</v>
+      </c>
+      <c r="H510" t="n">
+        <v>329.92</v>
+      </c>
+      <c r="I510" t="n">
+        <v>321.32</v>
+      </c>
+      <c r="J510" t="n">
+        <v>316.07</v>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20309,7 +20348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B567"/>
+  <dimension ref="A1:B568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25982,6 +26021,16 @@
       </c>
       <c r="B567" t="n">
         <v>-0.2</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
@@ -26150,28 +26199,28 @@
         <v>0.0541</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.480888285888625</v>
+        <v>-0.4814204446067358</v>
       </c>
       <c r="J2" t="n">
+        <v>509</v>
+      </c>
+      <c r="K2" t="n">
         <v>508</v>
       </c>
-      <c r="K2" t="n">
-        <v>507</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.3420342931278789</v>
+        <v>0.3434269909320944</v>
       </c>
       <c r="M2" t="n">
-        <v>3.728214386992021</v>
+        <v>3.723203477122812</v>
       </c>
       <c r="N2" t="n">
-        <v>22.96740545418251</v>
+        <v>22.92573873053574</v>
       </c>
       <c r="O2" t="n">
-        <v>4.792432102198477</v>
+        <v>4.788082991191334</v>
       </c>
       <c r="P2" t="n">
-        <v>322.4907949145731</v>
+        <v>322.496647380552</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26228,28 +26277,28 @@
         <v>0.0765</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3520862467774531</v>
+        <v>-0.3525859195345089</v>
       </c>
       <c r="J3" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K3" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2239270779817644</v>
+        <v>0.2251118664232549</v>
       </c>
       <c r="M3" t="n">
-        <v>3.337315760830808</v>
+        <v>3.333232246253689</v>
       </c>
       <c r="N3" t="n">
-        <v>22.35237733140326</v>
+        <v>22.31162372120165</v>
       </c>
       <c r="O3" t="n">
-        <v>4.727830086985283</v>
+        <v>4.723518150828008</v>
       </c>
       <c r="P3" t="n">
-        <v>323.1245969337037</v>
+        <v>323.1300648203473</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26306,28 +26355,28 @@
         <v>0.0696</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4589233365920491</v>
+        <v>-0.4601491236369663</v>
       </c>
       <c r="J4" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K4" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3676740097349981</v>
+        <v>0.3696370525129973</v>
       </c>
       <c r="M4" t="n">
-        <v>3.390709756230708</v>
+        <v>3.389472300054486</v>
       </c>
       <c r="N4" t="n">
-        <v>18.84464961699184</v>
+        <v>18.82664803064022</v>
       </c>
       <c r="O4" t="n">
-        <v>4.341042457404885</v>
+        <v>4.338968544555286</v>
       </c>
       <c r="P4" t="n">
-        <v>339.5812661797289</v>
+        <v>339.5946798880333</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26384,28 +26433,28 @@
         <v>0.0868</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5374031487259038</v>
+        <v>-0.537788830596144</v>
       </c>
       <c r="J5" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K5" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4389059492678949</v>
+        <v>0.4402477543243936</v>
       </c>
       <c r="M5" t="n">
-        <v>3.622656547449962</v>
+        <v>3.617237677997653</v>
       </c>
       <c r="N5" t="n">
-        <v>19.20853707794069</v>
+        <v>19.17268236338064</v>
       </c>
       <c r="O5" t="n">
-        <v>4.382754508062332</v>
+        <v>4.378662165933864</v>
       </c>
       <c r="P5" t="n">
-        <v>337.9662246862659</v>
+        <v>337.9704451780121</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26462,28 +26511,28 @@
         <v>0.0866</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5344293638055211</v>
+        <v>-0.5352578918106601</v>
       </c>
       <c r="J6" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K6" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3915038866008472</v>
+        <v>0.3931325277844656</v>
       </c>
       <c r="M6" t="n">
-        <v>3.91282638105298</v>
+        <v>3.907716621991587</v>
       </c>
       <c r="N6" t="n">
-        <v>23.09574817727314</v>
+        <v>23.05906352189325</v>
       </c>
       <c r="O6" t="n">
-        <v>4.805803593289383</v>
+        <v>4.801985372936203</v>
       </c>
       <c r="P6" t="n">
-        <v>336.8122857504809</v>
+        <v>336.8213522788221</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26540,28 +26589,28 @@
         <v>0.0736</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4392233978944427</v>
+        <v>-0.4404070851753376</v>
       </c>
       <c r="J7" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K7" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2738663277766804</v>
+        <v>0.2756248389893103</v>
       </c>
       <c r="M7" t="n">
-        <v>3.836021664902737</v>
+        <v>3.832529013333064</v>
       </c>
       <c r="N7" t="n">
-        <v>26.61206363060607</v>
+        <v>26.57751775957693</v>
       </c>
       <c r="O7" t="n">
-        <v>5.158688169545245</v>
+        <v>5.155338762833819</v>
       </c>
       <c r="P7" t="n">
-        <v>344.6676981748923</v>
+        <v>344.6806511882035</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26618,28 +26667,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3250418521771588</v>
+        <v>-0.3254672457144026</v>
       </c>
       <c r="J8" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K8" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1853577172620282</v>
+        <v>0.1863610743531153</v>
       </c>
       <c r="M8" t="n">
-        <v>3.593765799282663</v>
+        <v>3.587888828840232</v>
       </c>
       <c r="N8" t="n">
-        <v>24.15819731308105</v>
+        <v>24.1130260609675</v>
       </c>
       <c r="O8" t="n">
-        <v>4.915098911830874</v>
+        <v>4.91050160991395</v>
       </c>
       <c r="P8" t="n">
-        <v>339.5754349135441</v>
+        <v>339.5800899674924</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26696,28 +26745,28 @@
         <v>0.0692</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2683825429959009</v>
+        <v>-0.2699753966503798</v>
       </c>
       <c r="J9" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K9" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1291285844502497</v>
+        <v>0.1307875753895452</v>
       </c>
       <c r="M9" t="n">
-        <v>4.042971897835548</v>
+        <v>4.042538139790738</v>
       </c>
       <c r="N9" t="n">
-        <v>25.27375980131866</v>
+        <v>25.2562250417844</v>
       </c>
       <c r="O9" t="n">
-        <v>5.027301443251505</v>
+        <v>5.0255571871967</v>
       </c>
       <c r="P9" t="n">
-        <v>332.4531847237547</v>
+        <v>332.4706152182123</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26774,28 +26823,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.316666247106713</v>
+        <v>-0.3193965270950033</v>
       </c>
       <c r="J10" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K10" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1247869480368339</v>
+        <v>0.1268435778609097</v>
       </c>
       <c r="M10" t="n">
-        <v>5.033129120231743</v>
+        <v>5.03643195493466</v>
       </c>
       <c r="N10" t="n">
-        <v>36.59130119734033</v>
+        <v>36.61378054269672</v>
       </c>
       <c r="O10" t="n">
-        <v>6.049074408315732</v>
+        <v>6.050932204437323</v>
       </c>
       <c r="P10" t="n">
-        <v>331.3708575268927</v>
+        <v>331.4007348041114</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26833,7 +26882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K509"/>
+  <dimension ref="A1:K510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55845,6 +55894,63 @@
         </is>
       </c>
     </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:27:15+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>-46.61339881324027,168.83176220664762</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>-46.61281587823415,168.83206760045292</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>-46.612181813722536,168.8322900524116</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>-46.611546379492935,168.83233450705248</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>-46.61092557120715,168.83232999259712</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>-46.61029901397767,168.83216949967132</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>-46.60971305725661,168.8318669040217</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>-46.60912099329581,168.83158747031135</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>-46.60854338944177,168.8312706670996</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0553/nzd0553.xlsx
+++ b/data/nzd0553/nzd0553.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K510"/>
+  <dimension ref="A1:K511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20332,6 +20332,45 @@
         <v>316.07</v>
       </c>
       <c r="K510" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:14+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>309.33</v>
+      </c>
+      <c r="C511" t="n">
+        <v>313.3</v>
+      </c>
+      <c r="D511" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="E511" t="n">
+        <v>324.07</v>
+      </c>
+      <c r="F511" t="n">
+        <v>321.7</v>
+      </c>
+      <c r="G511" t="n">
+        <v>330.92</v>
+      </c>
+      <c r="H511" t="n">
+        <v>330.85</v>
+      </c>
+      <c r="I511" t="n">
+        <v>322.51</v>
+      </c>
+      <c r="J511" t="n">
+        <v>317.2</v>
+      </c>
+      <c r="K511" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -20348,7 +20387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B568"/>
+  <dimension ref="A1:B569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26031,6 +26070,16 @@
       </c>
       <c r="B568" t="n">
         <v>0.08</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>0.74</v>
       </c>
     </row>
   </sheetData>
@@ -26199,28 +26248,28 @@
         <v>0.0541</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4814204446067358</v>
+        <v>-0.4815965814350591</v>
       </c>
       <c r="J2" t="n">
+        <v>510</v>
+      </c>
+      <c r="K2" t="n">
         <v>509</v>
       </c>
-      <c r="K2" t="n">
-        <v>508</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.3434269909320944</v>
+        <v>0.3445194170486217</v>
       </c>
       <c r="M2" t="n">
-        <v>3.723203477122812</v>
+        <v>3.716658255343931</v>
       </c>
       <c r="N2" t="n">
-        <v>22.92573873053574</v>
+        <v>22.88108701690328</v>
       </c>
       <c r="O2" t="n">
-        <v>4.788082991191334</v>
+        <v>4.783417922041025</v>
       </c>
       <c r="P2" t="n">
-        <v>322.496647380552</v>
+        <v>322.4985881433907</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26277,28 +26326,28 @@
         <v>0.0765</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3525859195345089</v>
+        <v>-0.3527885252207067</v>
       </c>
       <c r="J3" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K3" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2251118664232549</v>
+        <v>0.2260267275344092</v>
       </c>
       <c r="M3" t="n">
-        <v>3.333232246253689</v>
+        <v>3.327693139142801</v>
       </c>
       <c r="N3" t="n">
-        <v>22.31162372120165</v>
+        <v>22.2683960287937</v>
       </c>
       <c r="O3" t="n">
-        <v>4.723518150828008</v>
+        <v>4.7189401382931</v>
       </c>
       <c r="P3" t="n">
-        <v>323.1300648203473</v>
+        <v>323.1322861628703</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26355,28 +26404,28 @@
         <v>0.0696</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4601491236369663</v>
+        <v>-0.4609885006367258</v>
       </c>
       <c r="J4" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K4" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3696370525129973</v>
+        <v>0.3713351962876678</v>
       </c>
       <c r="M4" t="n">
-        <v>3.389472300054486</v>
+        <v>3.386516179782744</v>
       </c>
       <c r="N4" t="n">
-        <v>18.82664803064022</v>
+        <v>18.79866827382673</v>
       </c>
       <c r="O4" t="n">
-        <v>4.338968544555286</v>
+        <v>4.335743105146651</v>
       </c>
       <c r="P4" t="n">
-        <v>339.5946798880333</v>
+        <v>339.6038827088296</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26433,28 +26482,28 @@
         <v>0.0868</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.537788830596144</v>
+        <v>-0.5376697927027776</v>
       </c>
       <c r="J5" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K5" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4402477543243936</v>
+        <v>0.4411497464230002</v>
       </c>
       <c r="M5" t="n">
-        <v>3.617237677997653</v>
+        <v>3.610807973283924</v>
       </c>
       <c r="N5" t="n">
-        <v>19.17268236338064</v>
+        <v>19.13526857452869</v>
       </c>
       <c r="O5" t="n">
-        <v>4.378662165933864</v>
+        <v>4.374387794255179</v>
       </c>
       <c r="P5" t="n">
-        <v>337.9704451780121</v>
+        <v>337.9691400619548</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26511,28 +26560,28 @@
         <v>0.0866</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5352578918106601</v>
+        <v>-0.5356445096990738</v>
       </c>
       <c r="J6" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K6" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3931325277844656</v>
+        <v>0.3944391041189278</v>
       </c>
       <c r="M6" t="n">
-        <v>3.907716621991587</v>
+        <v>3.901247528945487</v>
       </c>
       <c r="N6" t="n">
-        <v>23.05906352189325</v>
+        <v>23.01574531222034</v>
       </c>
       <c r="O6" t="n">
-        <v>4.801985372936203</v>
+        <v>4.797472804740048</v>
       </c>
       <c r="P6" t="n">
-        <v>336.8213522788221</v>
+        <v>336.825591107316</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26589,28 +26638,28 @@
         <v>0.0736</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4404070851753376</v>
+        <v>-0.4412434824644582</v>
       </c>
       <c r="J7" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K7" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2756248389893103</v>
+        <v>0.277139169439691</v>
       </c>
       <c r="M7" t="n">
-        <v>3.832529013333064</v>
+        <v>3.827850721355968</v>
       </c>
       <c r="N7" t="n">
-        <v>26.57751775957693</v>
+        <v>26.53427689303696</v>
       </c>
       <c r="O7" t="n">
-        <v>5.155338762833819</v>
+        <v>5.151143260775899</v>
       </c>
       <c r="P7" t="n">
-        <v>344.6806511882035</v>
+        <v>344.689821339838</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26667,28 +26716,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3254672457144026</v>
+        <v>-0.3255183102357028</v>
       </c>
       <c r="J8" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K8" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1863610743531153</v>
+        <v>0.1870328150680233</v>
       </c>
       <c r="M8" t="n">
-        <v>3.587888828840232</v>
+        <v>3.58099467542253</v>
       </c>
       <c r="N8" t="n">
-        <v>24.1130260609675</v>
+        <v>24.0657786874362</v>
       </c>
       <c r="O8" t="n">
-        <v>4.91050160991395</v>
+        <v>4.905688400972508</v>
       </c>
       <c r="P8" t="n">
-        <v>339.5800899674924</v>
+        <v>339.5806498322954</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26745,28 +26794,28 @@
         <v>0.0692</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2699753966503798</v>
+        <v>-0.2710847967923504</v>
       </c>
       <c r="J9" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K9" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1307875753895452</v>
+        <v>0.1321227504191042</v>
       </c>
       <c r="M9" t="n">
-        <v>4.042538139790738</v>
+        <v>4.039851842197817</v>
       </c>
       <c r="N9" t="n">
-        <v>25.2562250417844</v>
+        <v>25.2223117951766</v>
       </c>
       <c r="O9" t="n">
-        <v>5.0255571871967</v>
+        <v>5.02218197551389</v>
       </c>
       <c r="P9" t="n">
-        <v>332.4706152182123</v>
+        <v>332.4827785377945</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26823,28 +26872,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3193965270950033</v>
+        <v>-0.3216552878622244</v>
       </c>
       <c r="J10" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K10" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1268435778609097</v>
+        <v>0.1286751961683502</v>
       </c>
       <c r="M10" t="n">
-        <v>5.03643195493466</v>
+        <v>5.037428444279404</v>
       </c>
       <c r="N10" t="n">
-        <v>36.61378054269672</v>
+        <v>36.60669302501517</v>
       </c>
       <c r="O10" t="n">
-        <v>6.050932204437323</v>
+        <v>6.050346521069282</v>
       </c>
       <c r="P10" t="n">
-        <v>331.4007348041114</v>
+        <v>331.4254995648428</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26882,7 +26931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K510"/>
+  <dimension ref="A1:K511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55951,6 +56000,63 @@
         </is>
       </c>
     </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:14+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>-46.61339547687534,168.83175194375335</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>-46.612813078772355,168.83205898913783</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>-46.612179700581905,168.83227818171602</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>-46.61154602792512,168.83231808106186</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>-46.61092557173079,168.83231577612253</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>-46.610300158866856,168.8321585387459</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>-46.60971593829842,168.83185551786403</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>-46.609125158217836,168.83157317509765</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>-46.60854734434814,168.8312570927885</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0553/nzd0553.xlsx
+++ b/data/nzd0553/nzd0553.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K511"/>
+  <dimension ref="A1:K513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20373,6 +20373,84 @@
       <c r="K511" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:27:12+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>306.38</v>
+      </c>
+      <c r="C512" t="n">
+        <v>310.27</v>
+      </c>
+      <c r="D512" t="n">
+        <v>323.38</v>
+      </c>
+      <c r="E512" t="n">
+        <v>322.79</v>
+      </c>
+      <c r="F512" t="n">
+        <v>322.46</v>
+      </c>
+      <c r="G512" t="n">
+        <v>331.11</v>
+      </c>
+      <c r="H512" t="n">
+        <v>330.52</v>
+      </c>
+      <c r="I512" t="n">
+        <v>324.42</v>
+      </c>
+      <c r="J512" t="n">
+        <v>321.04</v>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:06+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>308.78</v>
+      </c>
+      <c r="C513" t="n">
+        <v>313.31</v>
+      </c>
+      <c r="D513" t="n">
+        <v>327.02</v>
+      </c>
+      <c r="E513" t="n">
+        <v>327.7</v>
+      </c>
+      <c r="F513" t="n">
+        <v>327.79</v>
+      </c>
+      <c r="G513" t="n">
+        <v>336.98</v>
+      </c>
+      <c r="H513" t="n">
+        <v>335.33</v>
+      </c>
+      <c r="I513" t="n">
+        <v>329.85</v>
+      </c>
+      <c r="J513" t="n">
+        <v>324.58</v>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20387,7 +20465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B569"/>
+  <dimension ref="A1:B571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26080,6 +26158,26 @@
       </c>
       <c r="B569" t="n">
         <v>0.74</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>-0.18</v>
       </c>
     </row>
   </sheetData>
@@ -26248,28 +26346,28 @@
         <v>0.0541</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4815965814350591</v>
+        <v>-0.4832676679280287</v>
       </c>
       <c r="J2" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K2" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3445194170486217</v>
+        <v>0.3477674204215321</v>
       </c>
       <c r="M2" t="n">
-        <v>3.716658255343931</v>
+        <v>3.709298554285485</v>
       </c>
       <c r="N2" t="n">
-        <v>22.88108701690328</v>
+        <v>22.81448947094599</v>
       </c>
       <c r="O2" t="n">
-        <v>4.783417922041025</v>
+        <v>4.776451556432452</v>
       </c>
       <c r="P2" t="n">
-        <v>322.4985881433907</v>
+        <v>322.5171288206628</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26326,28 +26424,28 @@
         <v>0.0765</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3527885252207067</v>
+        <v>-0.3543284737804346</v>
       </c>
       <c r="J3" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K3" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2260267275344092</v>
+        <v>0.2288435506933771</v>
       </c>
       <c r="M3" t="n">
-        <v>3.327693139142801</v>
+        <v>3.322127480854341</v>
       </c>
       <c r="N3" t="n">
-        <v>22.2683960287937</v>
+        <v>22.20534769545003</v>
       </c>
       <c r="O3" t="n">
-        <v>4.7189401382931</v>
+        <v>4.712255054159317</v>
       </c>
       <c r="P3" t="n">
-        <v>323.1322861628703</v>
+        <v>323.1492846633874</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26404,28 +26502,28 @@
         <v>0.0696</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4609885006367258</v>
+        <v>-0.4626771189463905</v>
       </c>
       <c r="J4" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K4" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3713351962876678</v>
+        <v>0.3746233362381599</v>
       </c>
       <c r="M4" t="n">
-        <v>3.386516179782744</v>
+        <v>3.380561650001013</v>
       </c>
       <c r="N4" t="n">
-        <v>18.79866827382673</v>
+        <v>18.75618650488228</v>
       </c>
       <c r="O4" t="n">
-        <v>4.335743105146651</v>
+        <v>4.330841316058842</v>
       </c>
       <c r="P4" t="n">
-        <v>339.6038827088296</v>
+        <v>339.622521003903</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26482,28 +26580,28 @@
         <v>0.0868</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5376697927027776</v>
+        <v>-0.5364298578191289</v>
       </c>
       <c r="J5" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K5" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4411497464230002</v>
+        <v>0.4416520667233169</v>
       </c>
       <c r="M5" t="n">
-        <v>3.610807973283924</v>
+        <v>3.607037677465771</v>
       </c>
       <c r="N5" t="n">
-        <v>19.13526857452869</v>
+        <v>19.09379188867798</v>
       </c>
       <c r="O5" t="n">
-        <v>4.374387794255179</v>
+        <v>4.36964436638475</v>
       </c>
       <c r="P5" t="n">
-        <v>337.9691400619548</v>
+        <v>337.9554233172715</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26560,28 +26658,28 @@
         <v>0.0866</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5356445096990738</v>
+        <v>-0.5336410019314288</v>
       </c>
       <c r="J6" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K6" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3944391041189278</v>
+        <v>0.3941057034723545</v>
       </c>
       <c r="M6" t="n">
-        <v>3.901247528945487</v>
+        <v>3.900263865075277</v>
       </c>
       <c r="N6" t="n">
-        <v>23.01574531222034</v>
+        <v>22.97863249751192</v>
       </c>
       <c r="O6" t="n">
-        <v>4.797472804740048</v>
+        <v>4.793603289542421</v>
       </c>
       <c r="P6" t="n">
-        <v>336.825591107316</v>
+        <v>336.8034379682055</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26638,28 +26736,28 @@
         <v>0.0736</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4412434824644582</v>
+        <v>-0.4403822173740295</v>
       </c>
       <c r="J7" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K7" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L7" t="n">
-        <v>0.277139169439691</v>
+        <v>0.277747806716461</v>
       </c>
       <c r="M7" t="n">
-        <v>3.827850721355968</v>
+        <v>3.825779108771562</v>
       </c>
       <c r="N7" t="n">
-        <v>26.53427689303696</v>
+        <v>26.46911569062161</v>
       </c>
       <c r="O7" t="n">
-        <v>5.151143260775899</v>
+        <v>5.144814446665848</v>
       </c>
       <c r="P7" t="n">
-        <v>344.689821339838</v>
+        <v>344.6802836427801</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26716,28 +26814,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3255183102357028</v>
+        <v>-0.3239386901418172</v>
       </c>
       <c r="J8" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K8" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1870328150680233</v>
+        <v>0.1865890685378225</v>
       </c>
       <c r="M8" t="n">
-        <v>3.58099467542253</v>
+        <v>3.579940247686249</v>
       </c>
       <c r="N8" t="n">
-        <v>24.0657786874362</v>
+        <v>24.00994165550487</v>
       </c>
       <c r="O8" t="n">
-        <v>4.905688400972508</v>
+        <v>4.899994046476473</v>
       </c>
       <c r="P8" t="n">
-        <v>339.5806498322954</v>
+        <v>339.5631812375474</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26794,28 +26892,28 @@
         <v>0.0692</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2710847967923504</v>
+        <v>-0.2696176934449059</v>
       </c>
       <c r="J9" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K9" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1321227504191042</v>
+        <v>0.1316493917566254</v>
       </c>
       <c r="M9" t="n">
-        <v>4.039851842197817</v>
+        <v>4.035111963240276</v>
       </c>
       <c r="N9" t="n">
-        <v>25.2223117951766</v>
+        <v>25.16602867956245</v>
       </c>
       <c r="O9" t="n">
-        <v>5.02218197551389</v>
+        <v>5.016575393588981</v>
       </c>
       <c r="P9" t="n">
-        <v>332.4827785377945</v>
+        <v>332.4665503423882</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26872,28 +26970,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3216552878622244</v>
+        <v>-0.3217016267856442</v>
       </c>
       <c r="J10" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K10" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1286751961683502</v>
+        <v>0.1296142106059383</v>
       </c>
       <c r="M10" t="n">
-        <v>5.037428444279404</v>
+        <v>5.024674045406015</v>
       </c>
       <c r="N10" t="n">
-        <v>36.60669302501517</v>
+        <v>36.47601116186995</v>
       </c>
       <c r="O10" t="n">
-        <v>6.050346521069282</v>
+        <v>6.039537330116435</v>
       </c>
       <c r="P10" t="n">
-        <v>331.4254995648428</v>
+        <v>331.4259970939059</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26931,7 +27029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K511"/>
+  <dimension ref="A1:K513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56057,6 +56155,120 @@
         </is>
       </c>
     </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:27:12+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>-46.61340678983331,168.8317867432278</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>-46.61282469845217,168.83209473199958</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>-46.61218401678278,168.83230242824422</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>-46.61154638507335,168.8323347677825</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>-46.610925572094835,168.83230586371835</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>-46.61030041478312,168.8321560886566</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>-46.60971491599339,168.83185955811368</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>-46.60913184308877,168.83155023067462</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>-46.608560784017385,168.83121096414195</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:06+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>-46.61339758607166,168.83175843178984</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>-46.61281304042356,168.8320588711746</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>-46.612175833981034,168.83225646087135</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>-46.61154501506181,168.8322707585672</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>-46.610925574623806,168.83223634646407</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>-46.61030832122237,168.83208039378363</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>-46.609729816848905,168.83180066840035</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>-46.60915084769563,168.83148500121212</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>-46.60857317369528,168.8311684392766</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0553/nzd0553.xlsx
+++ b/data/nzd0553/nzd0553.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K513"/>
+  <dimension ref="A1:K515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20449,6 +20449,84 @@
         <v>324.58</v>
       </c>
       <c r="K513" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:26:54+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>309.07</v>
+      </c>
+      <c r="C514" t="n">
+        <v>313.49</v>
+      </c>
+      <c r="D514" t="n">
+        <v>326.67</v>
+      </c>
+      <c r="E514" t="n">
+        <v>327.34</v>
+      </c>
+      <c r="F514" t="n">
+        <v>327.91</v>
+      </c>
+      <c r="G514" t="n">
+        <v>337.64</v>
+      </c>
+      <c r="H514" t="n">
+        <v>336.18</v>
+      </c>
+      <c r="I514" t="n">
+        <v>330.53</v>
+      </c>
+      <c r="J514" t="n">
+        <v>327.17</v>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:42+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>309.02</v>
+      </c>
+      <c r="C515" t="n">
+        <v>313.36</v>
+      </c>
+      <c r="D515" t="n">
+        <v>326.38</v>
+      </c>
+      <c r="E515" t="n">
+        <v>326.83</v>
+      </c>
+      <c r="F515" t="n">
+        <v>327.45</v>
+      </c>
+      <c r="G515" t="n">
+        <v>337.51</v>
+      </c>
+      <c r="H515" t="n">
+        <v>335.64</v>
+      </c>
+      <c r="I515" t="n">
+        <v>330.31</v>
+      </c>
+      <c r="J515" t="n">
+        <v>327.91</v>
+      </c>
+      <c r="K515" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20465,7 +20543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B571"/>
+  <dimension ref="A1:B573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26178,6 +26256,26 @@
       </c>
       <c r="B571" t="n">
         <v>-0.18</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>-1.12</v>
       </c>
     </row>
   </sheetData>
@@ -26346,28 +26444,28 @@
         <v>0.0541</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4832676679280287</v>
+        <v>-0.4837348051247847</v>
       </c>
       <c r="J2" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K2" t="n">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3477674204215321</v>
+        <v>0.3501011410180848</v>
       </c>
       <c r="M2" t="n">
-        <v>3.709298554285485</v>
+        <v>3.696833019900506</v>
       </c>
       <c r="N2" t="n">
-        <v>22.81448947094599</v>
+        <v>22.72689840550555</v>
       </c>
       <c r="O2" t="n">
-        <v>4.776451556432452</v>
+        <v>4.767273686868161</v>
       </c>
       <c r="P2" t="n">
-        <v>322.5171288206628</v>
+        <v>322.5223291580623</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26424,28 +26522,28 @@
         <v>0.0765</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3543284737804346</v>
+        <v>-0.3545460500501147</v>
       </c>
       <c r="J3" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K3" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2288435506933771</v>
+        <v>0.2305390526989278</v>
       </c>
       <c r="M3" t="n">
-        <v>3.322127480854341</v>
+        <v>3.310238215052589</v>
       </c>
       <c r="N3" t="n">
-        <v>22.20534769545003</v>
+        <v>22.11925515438747</v>
       </c>
       <c r="O3" t="n">
-        <v>4.712255054159317</v>
+        <v>4.703111220712038</v>
       </c>
       <c r="P3" t="n">
-        <v>323.1492846633874</v>
+        <v>323.1516953860241</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26502,28 +26600,28 @@
         <v>0.0696</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4626771189463905</v>
+        <v>-0.4632788021940205</v>
       </c>
       <c r="J4" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K4" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3746233362381599</v>
+        <v>0.3771670533995068</v>
       </c>
       <c r="M4" t="n">
-        <v>3.380561650001013</v>
+        <v>3.369965226604669</v>
       </c>
       <c r="N4" t="n">
-        <v>18.75618650488228</v>
+        <v>18.68554649914472</v>
       </c>
       <c r="O4" t="n">
-        <v>4.330841316058842</v>
+        <v>4.322678162799622</v>
       </c>
       <c r="P4" t="n">
-        <v>339.622521003903</v>
+        <v>339.6291873945909</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26580,28 +26678,28 @@
         <v>0.0868</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5364298578191289</v>
+        <v>-0.5337441113375277</v>
       </c>
       <c r="J5" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K5" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4416520667233169</v>
+        <v>0.4406514965156588</v>
       </c>
       <c r="M5" t="n">
-        <v>3.607037677465771</v>
+        <v>3.607812950355724</v>
       </c>
       <c r="N5" t="n">
-        <v>19.09379188867798</v>
+        <v>19.06498823042921</v>
       </c>
       <c r="O5" t="n">
-        <v>4.36964436638475</v>
+        <v>4.366347241165001</v>
       </c>
       <c r="P5" t="n">
-        <v>337.9554233172715</v>
+        <v>337.925673650746</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26658,28 +26756,28 @@
         <v>0.0866</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5336410019314288</v>
+        <v>-0.5296464340573671</v>
       </c>
       <c r="J6" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K6" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3941057034723545</v>
+        <v>0.3914748089738547</v>
       </c>
       <c r="M6" t="n">
-        <v>3.900263865075277</v>
+        <v>3.912532128701862</v>
       </c>
       <c r="N6" t="n">
-        <v>22.97863249751192</v>
+        <v>22.98952314098101</v>
       </c>
       <c r="O6" t="n">
-        <v>4.793603289542421</v>
+        <v>4.794739110836064</v>
       </c>
       <c r="P6" t="n">
-        <v>336.8034379682055</v>
+        <v>336.7591894441888</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26736,28 +26834,28 @@
         <v>0.0736</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4403822173740295</v>
+        <v>-0.4367553435674536</v>
       </c>
       <c r="J7" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K7" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L7" t="n">
-        <v>0.277747806716461</v>
+        <v>0.2754874493914751</v>
       </c>
       <c r="M7" t="n">
-        <v>3.825779108771562</v>
+        <v>3.834445193070616</v>
       </c>
       <c r="N7" t="n">
-        <v>26.46911569062161</v>
+        <v>26.44865955606096</v>
       </c>
       <c r="O7" t="n">
-        <v>5.144814446665848</v>
+        <v>5.142826028173708</v>
       </c>
       <c r="P7" t="n">
-        <v>344.6802836427801</v>
+        <v>344.6401069317398</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26814,28 +26912,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3239386901418172</v>
+        <v>-0.3200394811441605</v>
       </c>
       <c r="J8" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K8" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1865890685378225</v>
+        <v>0.1835961299336872</v>
       </c>
       <c r="M8" t="n">
-        <v>3.579940247686249</v>
+        <v>3.59398111326086</v>
       </c>
       <c r="N8" t="n">
-        <v>24.00994165550487</v>
+        <v>24.01218965707268</v>
       </c>
       <c r="O8" t="n">
-        <v>4.899994046476473</v>
+        <v>4.900223429301228</v>
       </c>
       <c r="P8" t="n">
-        <v>339.5631812375474</v>
+        <v>339.5199894691993</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26892,28 +26990,28 @@
         <v>0.0692</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2696176934449059</v>
+        <v>-0.2655966795261754</v>
       </c>
       <c r="J9" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K9" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1316493917566254</v>
+        <v>0.1287365373695114</v>
       </c>
       <c r="M9" t="n">
-        <v>4.035111963240276</v>
+        <v>4.040452813150563</v>
       </c>
       <c r="N9" t="n">
-        <v>25.16602867956245</v>
+        <v>25.16958632264615</v>
       </c>
       <c r="O9" t="n">
-        <v>5.016575393588981</v>
+        <v>5.016929969876613</v>
       </c>
       <c r="P9" t="n">
-        <v>332.4665503423882</v>
+        <v>332.4220078888432</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26970,28 +27068,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3217016267856442</v>
+        <v>-0.3180287580979445</v>
       </c>
       <c r="J10" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K10" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1296142106059383</v>
+        <v>0.1277154187326104</v>
       </c>
       <c r="M10" t="n">
-        <v>5.024674045406015</v>
+        <v>5.023848789076676</v>
       </c>
       <c r="N10" t="n">
-        <v>36.47601116186995</v>
+        <v>36.41923072595363</v>
       </c>
       <c r="O10" t="n">
-        <v>6.039537330116435</v>
+        <v>6.034834772050817</v>
       </c>
       <c r="P10" t="n">
-        <v>331.4259970939059</v>
+        <v>331.3853071617574</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27029,7 +27127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K513"/>
+  <dimension ref="A1:K515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56269,6 +56367,120 @@
         </is>
       </c>
     </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:26:54+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>-46.61339647395,168.83175501082508</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>-46.612812350145205,168.8320567478368</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>-46.61217662078969,168.8322608808104</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>-46.611545115511944,168.83227545170703</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>-46.610925574680266,168.8322347813477</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>-46.6103092101885,168.83207188294494</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>-46.609732450052945,168.83179026169108</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>-46.60915322764367,168.83147683251022</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>-46.60858223844915,168.8311373264396</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:42+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>-46.61339666569512,168.83175560064657</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>-46.61281284867957,168.83205828135857</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>-46.61217727271672,168.8322645430457</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>-46.61154525781595,168.83228210032183</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>-46.610925574463764,168.83224078096052</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>-46.61030903508915,168.83207355932228</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>-46.60973077719402,168.83179687301237</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>-46.609152457660535,168.83147947532564</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>-46.60858482837721,168.8311284370558</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0553/nzd0553.xlsx
+++ b/data/nzd0553/nzd0553.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K515"/>
+  <dimension ref="A1:K516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20527,6 +20527,45 @@
         <v>327.91</v>
       </c>
       <c r="K515" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-12 22:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>307.89</v>
+      </c>
+      <c r="C516" t="n">
+        <v>313.54</v>
+      </c>
+      <c r="D516" t="n">
+        <v>325.55</v>
+      </c>
+      <c r="E516" t="n">
+        <v>326.54</v>
+      </c>
+      <c r="F516" t="n">
+        <v>327.25</v>
+      </c>
+      <c r="G516" t="n">
+        <v>337.24</v>
+      </c>
+      <c r="H516" t="n">
+        <v>335.12</v>
+      </c>
+      <c r="I516" t="n">
+        <v>329.87</v>
+      </c>
+      <c r="J516" t="n">
+        <v>327.33</v>
+      </c>
+      <c r="K516" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20543,7 +20582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B573"/>
+  <dimension ref="A1:B574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26276,6 +26315,16 @@
       </c>
       <c r="B573" t="n">
         <v>-1.12</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-04-12 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>0.71</v>
       </c>
     </row>
   </sheetData>
@@ -26444,28 +26493,28 @@
         <v>0.0541</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4837348051247847</v>
+        <v>-0.4844061583354634</v>
       </c>
       <c r="J2" t="n">
+        <v>515</v>
+      </c>
+      <c r="K2" t="n">
         <v>514</v>
       </c>
-      <c r="K2" t="n">
-        <v>513</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.3501011410180848</v>
+        <v>0.3516372382454911</v>
       </c>
       <c r="M2" t="n">
-        <v>3.696833019900506</v>
+        <v>3.692478659459022</v>
       </c>
       <c r="N2" t="n">
-        <v>22.72689840550555</v>
+        <v>22.68827543599275</v>
       </c>
       <c r="O2" t="n">
-        <v>4.767273686868161</v>
+        <v>4.763221119787822</v>
       </c>
       <c r="P2" t="n">
-        <v>322.5223291580623</v>
+        <v>322.5298295802277</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26522,28 +26571,28 @@
         <v>0.0765</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3545460500501147</v>
+        <v>-0.3545983715712302</v>
       </c>
       <c r="J3" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K3" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2305390526989278</v>
+        <v>0.2313374142367749</v>
       </c>
       <c r="M3" t="n">
-        <v>3.310238215052589</v>
+        <v>3.304057598067917</v>
       </c>
       <c r="N3" t="n">
-        <v>22.11925515438747</v>
+        <v>22.07633950020334</v>
       </c>
       <c r="O3" t="n">
-        <v>4.703111220712038</v>
+        <v>4.69854653059894</v>
       </c>
       <c r="P3" t="n">
-        <v>323.1516953860241</v>
+        <v>323.1522770828172</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26600,28 +26649,28 @@
         <v>0.0696</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4632788021940205</v>
+        <v>-0.4639413593565841</v>
       </c>
       <c r="J4" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K4" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3771670533995068</v>
+        <v>0.3787574206905553</v>
       </c>
       <c r="M4" t="n">
-        <v>3.369965226604669</v>
+        <v>3.366208143537674</v>
       </c>
       <c r="N4" t="n">
-        <v>18.68554649914472</v>
+        <v>18.65477305691237</v>
       </c>
       <c r="O4" t="n">
-        <v>4.322678162799622</v>
+        <v>4.319117161748726</v>
       </c>
       <c r="P4" t="n">
-        <v>339.6291873945909</v>
+        <v>339.6365535293766</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26678,28 +26727,28 @@
         <v>0.0868</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5337441113375277</v>
+        <v>-0.5326120169896913</v>
       </c>
       <c r="J5" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K5" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4406514965156588</v>
+        <v>0.4404321503682492</v>
       </c>
       <c r="M5" t="n">
-        <v>3.607812950355724</v>
+        <v>3.606993692717543</v>
       </c>
       <c r="N5" t="n">
-        <v>19.06498823042921</v>
+        <v>19.04405323692612</v>
       </c>
       <c r="O5" t="n">
-        <v>4.366347241165001</v>
+        <v>4.363949270663687</v>
       </c>
       <c r="P5" t="n">
-        <v>337.925673650746</v>
+        <v>337.9130873260825</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26756,28 +26805,28 @@
         <v>0.0866</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5296464340573671</v>
+        <v>-0.5278224424140828</v>
       </c>
       <c r="J6" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K6" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3914748089738547</v>
+        <v>0.3903995387846531</v>
       </c>
       <c r="M6" t="n">
-        <v>3.912532128701862</v>
+        <v>3.917406236998581</v>
       </c>
       <c r="N6" t="n">
-        <v>22.98952314098101</v>
+        <v>22.98663606467468</v>
       </c>
       <c r="O6" t="n">
-        <v>4.794739110836064</v>
+        <v>4.794438034292933</v>
       </c>
       <c r="P6" t="n">
-        <v>336.7591894441888</v>
+        <v>336.7389107889248</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26834,28 +26883,28 @@
         <v>0.0736</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4367553435674536</v>
+        <v>-0.435079338029826</v>
       </c>
       <c r="J7" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K7" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2754874493914751</v>
+        <v>0.2745259362196171</v>
       </c>
       <c r="M7" t="n">
-        <v>3.834445193070616</v>
+        <v>3.837786593793269</v>
       </c>
       <c r="N7" t="n">
-        <v>26.44865955606096</v>
+        <v>26.43255548655155</v>
       </c>
       <c r="O7" t="n">
-        <v>5.142826028173708</v>
+        <v>5.141260106875701</v>
       </c>
       <c r="P7" t="n">
-        <v>344.6401069317398</v>
+        <v>344.6214735467442</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26912,28 +26961,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3200394811441605</v>
+        <v>-0.3184084476595253</v>
       </c>
       <c r="J8" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K8" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1835961299336872</v>
+        <v>0.1824881612521662</v>
       </c>
       <c r="M8" t="n">
-        <v>3.59398111326086</v>
+        <v>3.598671425826951</v>
       </c>
       <c r="N8" t="n">
-        <v>24.01218965707268</v>
+        <v>23.99895012419494</v>
       </c>
       <c r="O8" t="n">
-        <v>4.900223429301228</v>
+        <v>4.898872331893835</v>
       </c>
       <c r="P8" t="n">
-        <v>339.5199894691993</v>
+        <v>339.5018560715599</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26990,28 +27039,28 @@
         <v>0.0692</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2655966795261754</v>
+        <v>-0.2638143192516288</v>
       </c>
       <c r="J9" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K9" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1287365373695114</v>
+        <v>0.1275243420677654</v>
       </c>
       <c r="M9" t="n">
-        <v>4.040452813150563</v>
+        <v>4.041890088635268</v>
       </c>
       <c r="N9" t="n">
-        <v>25.16958632264615</v>
+        <v>25.1605819076779</v>
       </c>
       <c r="O9" t="n">
-        <v>5.016929969876613</v>
+        <v>5.016032486704796</v>
       </c>
       <c r="P9" t="n">
-        <v>332.4220078888432</v>
+        <v>332.4021920800939</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27068,28 +27117,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3180287580979445</v>
+        <v>-0.3162846255337391</v>
       </c>
       <c r="J10" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K10" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1277154187326104</v>
+        <v>0.1268438074791646</v>
       </c>
       <c r="M10" t="n">
-        <v>5.023848789076676</v>
+        <v>5.02291276860192</v>
       </c>
       <c r="N10" t="n">
-        <v>36.41923072595363</v>
+        <v>36.38669049482261</v>
       </c>
       <c r="O10" t="n">
-        <v>6.034834772050817</v>
+        <v>6.032138136251739</v>
       </c>
       <c r="P10" t="n">
-        <v>331.3853071617574</v>
+        <v>331.3659163585515</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27127,7 +27176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K515"/>
+  <dimension ref="A1:K516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56481,6 +56530,63 @@
         </is>
       </c>
     </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-12 22:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>-46.61340099913406,168.83176893061358</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>-46.61281215840122,168.83205615802078</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>-46.61217913857622,168.83227502461628</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>-46.61154533873375,168.83228588090677</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>-46.61092557436952,168.83224338948781</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>-46.610308671421215,168.83207704102904</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>-46.60972916629246,168.83180323946956</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>-46.60915091769411,168.8314847609562</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>-46.608582798433645,168.83113540441076</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0553/nzd0553.xlsx
+++ b/data/nzd0553/nzd0553.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K516"/>
+  <dimension ref="A1:K519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20568,6 +20568,123 @@
       <c r="K516" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>307.89</v>
+      </c>
+      <c r="C517" t="n">
+        <v>313.54</v>
+      </c>
+      <c r="D517" t="n">
+        <v>325.55</v>
+      </c>
+      <c r="E517" t="n">
+        <v>326.54</v>
+      </c>
+      <c r="F517" t="n">
+        <v>327.25</v>
+      </c>
+      <c r="G517" t="n">
+        <v>337.24</v>
+      </c>
+      <c r="H517" t="n">
+        <v>335.12</v>
+      </c>
+      <c r="I517" t="n">
+        <v>328.22</v>
+      </c>
+      <c r="J517" t="n">
+        <v>325.67</v>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>309.2</v>
+      </c>
+      <c r="C518" t="n">
+        <v>314.83</v>
+      </c>
+      <c r="D518" t="n">
+        <v>326.86</v>
+      </c>
+      <c r="E518" t="n">
+        <v>326.38</v>
+      </c>
+      <c r="F518" t="n">
+        <v>326.82</v>
+      </c>
+      <c r="G518" t="n">
+        <v>336.78</v>
+      </c>
+      <c r="H518" t="n">
+        <v>334.55</v>
+      </c>
+      <c r="I518" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="J518" t="n">
+        <v>324.43</v>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>310.21</v>
+      </c>
+      <c r="C519" t="n">
+        <v>315.42</v>
+      </c>
+      <c r="D519" t="n">
+        <v>328.1</v>
+      </c>
+      <c r="E519" t="n">
+        <v>326.31</v>
+      </c>
+      <c r="F519" t="n">
+        <v>327.01</v>
+      </c>
+      <c r="G519" t="n">
+        <v>336.43</v>
+      </c>
+      <c r="H519" t="n">
+        <v>334.73</v>
+      </c>
+      <c r="I519" t="n">
+        <v>328.5</v>
+      </c>
+      <c r="J519" t="n">
+        <v>324.44</v>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20582,7 +20699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B574"/>
+  <dimension ref="A1:B577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26325,6 +26442,36 @@
       </c>
       <c r="B574" t="n">
         <v>0.71</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>0.13</v>
       </c>
     </row>
   </sheetData>
@@ -26493,28 +26640,28 @@
         <v>0.0541</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4844061583354634</v>
+        <v>-0.4849206466825765</v>
       </c>
       <c r="J2" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K2" t="n">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3516372382454911</v>
+        <v>0.3549411652372215</v>
       </c>
       <c r="M2" t="n">
-        <v>3.692478659459022</v>
+        <v>3.675854307890654</v>
       </c>
       <c r="N2" t="n">
-        <v>22.68827543599275</v>
+        <v>22.5630787488006</v>
       </c>
       <c r="O2" t="n">
-        <v>4.763221119787822</v>
+        <v>4.750060920535714</v>
       </c>
       <c r="P2" t="n">
-        <v>322.5298295802277</v>
+        <v>322.5355855007944</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26571,28 +26718,28 @@
         <v>0.0765</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3545983715712302</v>
+        <v>-0.3534895616896794</v>
       </c>
       <c r="J3" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K3" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2313374142367749</v>
+        <v>0.2323905680758336</v>
       </c>
       <c r="M3" t="n">
-        <v>3.304057598067917</v>
+        <v>3.291102338379573</v>
       </c>
       <c r="N3" t="n">
-        <v>22.07633950020334</v>
+        <v>21.95727743379651</v>
       </c>
       <c r="O3" t="n">
-        <v>4.69854653059894</v>
+        <v>4.6858593058047</v>
       </c>
       <c r="P3" t="n">
-        <v>323.1522770828172</v>
+        <v>323.1399030579165</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26649,28 +26796,28 @@
         <v>0.0696</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4639413593565841</v>
+        <v>-0.4643565250391451</v>
       </c>
       <c r="J4" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K4" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3787574206905553</v>
+        <v>0.3820531763610941</v>
       </c>
       <c r="M4" t="n">
-        <v>3.366208143537674</v>
+        <v>3.351992893294954</v>
       </c>
       <c r="N4" t="n">
-        <v>18.65477305691237</v>
+        <v>18.55384359262916</v>
       </c>
       <c r="O4" t="n">
-        <v>4.319117161748726</v>
+        <v>4.307417276353565</v>
       </c>
       <c r="P4" t="n">
-        <v>339.6365535293766</v>
+        <v>339.6411732795895</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26727,28 +26874,28 @@
         <v>0.0868</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5326120169896913</v>
+        <v>-0.5293781791099803</v>
       </c>
       <c r="J5" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K5" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4404321503682492</v>
+        <v>0.4399579713091208</v>
       </c>
       <c r="M5" t="n">
-        <v>3.606993692717543</v>
+        <v>3.603595825507913</v>
       </c>
       <c r="N5" t="n">
-        <v>19.04405323692612</v>
+        <v>18.97776207241036</v>
       </c>
       <c r="O5" t="n">
-        <v>4.363949270663687</v>
+        <v>4.356347331470524</v>
       </c>
       <c r="P5" t="n">
-        <v>337.9130873260825</v>
+        <v>337.8770237501587</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26805,28 +26952,28 @@
         <v>0.0866</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5278224424140828</v>
+        <v>-0.5226566015604581</v>
       </c>
       <c r="J6" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K6" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3903995387846531</v>
+        <v>0.3875482586697453</v>
       </c>
       <c r="M6" t="n">
-        <v>3.917406236998581</v>
+        <v>3.929766308146598</v>
       </c>
       <c r="N6" t="n">
-        <v>22.98663606467468</v>
+        <v>22.96584667380413</v>
       </c>
       <c r="O6" t="n">
-        <v>4.794438034292933</v>
+        <v>4.792269470074082</v>
       </c>
       <c r="P6" t="n">
-        <v>336.7389107889248</v>
+        <v>336.6813017377954</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26883,28 +27030,28 @@
         <v>0.0736</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.435079338029826</v>
+        <v>-0.4305920586032052</v>
       </c>
       <c r="J7" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K7" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2745259362196171</v>
+        <v>0.2722620751821178</v>
       </c>
       <c r="M7" t="n">
-        <v>3.837786593793269</v>
+        <v>3.844214604871371</v>
       </c>
       <c r="N7" t="n">
-        <v>26.43255548655155</v>
+        <v>26.36473351668164</v>
       </c>
       <c r="O7" t="n">
-        <v>5.141260106875701</v>
+        <v>5.134660019580814</v>
       </c>
       <c r="P7" t="n">
-        <v>344.6214735467442</v>
+        <v>344.5714336565487</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26961,28 +27108,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3184084476595253</v>
+        <v>-0.3139451012499661</v>
       </c>
       <c r="J8" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K8" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1824881612521662</v>
+        <v>0.1796451702528223</v>
       </c>
       <c r="M8" t="n">
-        <v>3.598671425826951</v>
+        <v>3.609407018930656</v>
       </c>
       <c r="N8" t="n">
-        <v>23.99895012419494</v>
+        <v>23.9440224911018</v>
       </c>
       <c r="O8" t="n">
-        <v>4.898872331893835</v>
+        <v>4.893262969747467</v>
       </c>
       <c r="P8" t="n">
-        <v>339.5018560715599</v>
+        <v>339.4520821999751</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27039,28 +27186,28 @@
         <v>0.0692</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2638143192516288</v>
+        <v>-0.2604874053181223</v>
       </c>
       <c r="J9" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K9" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1275243420677654</v>
+        <v>0.1259000735635919</v>
       </c>
       <c r="M9" t="n">
-        <v>4.041890088635268</v>
+        <v>4.035718605496619</v>
       </c>
       <c r="N9" t="n">
-        <v>25.1605819076779</v>
+        <v>25.06178823924316</v>
       </c>
       <c r="O9" t="n">
-        <v>5.016032486704796</v>
+        <v>5.006175010848418</v>
       </c>
       <c r="P9" t="n">
-        <v>332.4021920800939</v>
+        <v>332.3650896046479</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27117,28 +27264,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3162846255337391</v>
+        <v>-0.3140014115811269</v>
       </c>
       <c r="J10" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K10" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1268438074791646</v>
+        <v>0.1265592125453767</v>
       </c>
       <c r="M10" t="n">
-        <v>5.02291276860192</v>
+        <v>5.005227473888966</v>
       </c>
       <c r="N10" t="n">
-        <v>36.38669049482261</v>
+        <v>36.19981924746612</v>
       </c>
       <c r="O10" t="n">
-        <v>6.032138136251739</v>
+        <v>6.016628561533953</v>
       </c>
       <c r="P10" t="n">
-        <v>331.3659163585515</v>
+        <v>331.3404597118676</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27176,7 +27323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K516"/>
+  <dimension ref="A1:K519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56587,6 +56734,177 @@
         </is>
       </c>
     </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>-46.61340099913406,168.83176893061358</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>-46.61281215840122,168.83205615802078</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>-46.61217913857622,168.83227502461628</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>-46.61154533873375,168.83228588090677</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>-46.61092557436952,168.83224338948781</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>-46.610308671421215,168.83207704102904</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>-46.60972916629246,168.83180323946956</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>-46.60914514281771,168.83150458206825</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>-46.608576988592766,168.83115534545837</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>-46.613395975412686,168.8317534772892</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>-46.61280721140521,168.83204094076817</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>-46.61217619366501,168.8322584814149</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>-46.611545383378015,168.83228796674675</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>-46.61092557416672,168.83224899782158</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>-46.61030805183856,168.83208297282562</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>-46.60972740049609,168.83181021808565</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>-46.60914384784494,168.8315090268019</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>-46.60857264870926,168.83117024117803</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>-46.61339210216048,168.83174156289613</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>-46.61280494882499,168.83203398094042</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>-46.61217340611331,168.83224282220317</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>-46.61154540290985,168.83228887930173</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>-46.61092557425636,168.8322465197206</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>-46.61030758041675,168.83208748614902</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>-46.609727958116046,168.83180801431223</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>-46.60914612279699,168.83150121848587</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>-46.60857268370833,168.8311701210513</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0553/nzd0553.xlsx
+++ b/data/nzd0553/nzd0553.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K519"/>
+  <dimension ref="A1:K522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20685,6 +20685,123 @@
       <c r="K519" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>312.32</v>
+      </c>
+      <c r="C520" t="n">
+        <v>317.65</v>
+      </c>
+      <c r="D520" t="n">
+        <v>329.87</v>
+      </c>
+      <c r="E520" t="n">
+        <v>327.1</v>
+      </c>
+      <c r="F520" t="n">
+        <v>328.19</v>
+      </c>
+      <c r="G520" t="n">
+        <v>337.77</v>
+      </c>
+      <c r="H520" t="n">
+        <v>335.33</v>
+      </c>
+      <c r="I520" t="n">
+        <v>329.39</v>
+      </c>
+      <c r="J520" t="n">
+        <v>325.27</v>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>311.28</v>
+      </c>
+      <c r="C521" t="n">
+        <v>317</v>
+      </c>
+      <c r="D521" t="n">
+        <v>328.92</v>
+      </c>
+      <c r="E521" t="n">
+        <v>325.44</v>
+      </c>
+      <c r="F521" t="n">
+        <v>321.97</v>
+      </c>
+      <c r="G521" t="n">
+        <v>332.07</v>
+      </c>
+      <c r="H521" t="n">
+        <v>329.62</v>
+      </c>
+      <c r="I521" t="n">
+        <v>324.14</v>
+      </c>
+      <c r="J521" t="n">
+        <v>322.45</v>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>310.03</v>
+      </c>
+      <c r="C522" t="n">
+        <v>315.16</v>
+      </c>
+      <c r="D522" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="E522" t="n">
+        <v>324.43</v>
+      </c>
+      <c r="F522" t="n">
+        <v>321.26</v>
+      </c>
+      <c r="G522" t="n">
+        <v>331.64</v>
+      </c>
+      <c r="H522" t="n">
+        <v>328.76</v>
+      </c>
+      <c r="I522" t="n">
+        <v>323.42</v>
+      </c>
+      <c r="J522" t="n">
+        <v>321.29</v>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20699,7 +20816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B577"/>
+  <dimension ref="A1:B580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26472,6 +26589,36 @@
       </c>
       <c r="B577" t="n">
         <v>0.13</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>0.82</v>
       </c>
     </row>
   </sheetData>
@@ -26640,28 +26787,28 @@
         <v>0.0541</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4849206466825765</v>
+        <v>-0.482913188203343</v>
       </c>
       <c r="J2" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="K2" t="n">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3549411652372215</v>
+        <v>0.3556942910345259</v>
       </c>
       <c r="M2" t="n">
-        <v>3.675854307890654</v>
+        <v>3.665893460637756</v>
       </c>
       <c r="N2" t="n">
-        <v>22.5630787488006</v>
+        <v>22.45484208285229</v>
       </c>
       <c r="O2" t="n">
-        <v>4.750060920535714</v>
+        <v>4.738654037050215</v>
       </c>
       <c r="P2" t="n">
-        <v>322.5355855007944</v>
+        <v>322.5130024178188</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26718,28 +26865,28 @@
         <v>0.0765</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3534895616896794</v>
+        <v>-0.350054057093675</v>
       </c>
       <c r="J3" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="K3" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2323905680758336</v>
+        <v>0.2306816210676387</v>
       </c>
       <c r="M3" t="n">
-        <v>3.291102338379573</v>
+        <v>3.289707070940224</v>
       </c>
       <c r="N3" t="n">
-        <v>21.95727743379651</v>
+        <v>21.8874104639801</v>
       </c>
       <c r="O3" t="n">
-        <v>4.6858593058047</v>
+        <v>4.678398279751319</v>
       </c>
       <c r="P3" t="n">
-        <v>323.1399030579165</v>
+        <v>323.1014357054439</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26796,28 +26943,28 @@
         <v>0.0696</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4643565250391451</v>
+        <v>-0.4623544643013588</v>
       </c>
       <c r="J4" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="K4" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3820531763610941</v>
+        <v>0.3827004049497404</v>
       </c>
       <c r="M4" t="n">
-        <v>3.351992893294954</v>
+        <v>3.344046096197301</v>
       </c>
       <c r="N4" t="n">
-        <v>18.55384359262916</v>
+        <v>18.46792998767182</v>
       </c>
       <c r="O4" t="n">
-        <v>4.307417276353565</v>
+        <v>4.297432953249162</v>
       </c>
       <c r="P4" t="n">
-        <v>339.6411732795895</v>
+        <v>339.6187584032593</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26874,28 +27021,28 @@
         <v>0.0868</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5293781791099803</v>
+        <v>-0.5270380936205468</v>
       </c>
       <c r="J5" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="K5" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4399579713091208</v>
+        <v>0.4404643447720933</v>
       </c>
       <c r="M5" t="n">
-        <v>3.603595825507913</v>
+        <v>3.595362968043536</v>
       </c>
       <c r="N5" t="n">
-        <v>18.97776207241036</v>
+        <v>18.89870558916355</v>
       </c>
       <c r="O5" t="n">
-        <v>4.356347331470524</v>
+        <v>4.347264149918147</v>
       </c>
       <c r="P5" t="n">
-        <v>337.8770237501587</v>
+        <v>337.8508256110297</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26952,28 +27099,28 @@
         <v>0.0866</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5226566015604581</v>
+        <v>-0.5212833372164422</v>
       </c>
       <c r="J6" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="K6" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3875482586697453</v>
+        <v>0.3886096251317624</v>
       </c>
       <c r="M6" t="n">
-        <v>3.929766308146598</v>
+        <v>3.92416373832319</v>
       </c>
       <c r="N6" t="n">
-        <v>22.96584667380413</v>
+        <v>22.89727334114368</v>
       </c>
       <c r="O6" t="n">
-        <v>4.792269470074082</v>
+        <v>4.78510954327523</v>
       </c>
       <c r="P6" t="n">
-        <v>336.6813017377954</v>
+        <v>336.6659485221513</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27030,28 +27177,28 @@
         <v>0.0736</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4305920586032052</v>
+        <v>-0.4296195939566136</v>
       </c>
       <c r="J7" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="K7" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2722620751821178</v>
+        <v>0.2734797965457666</v>
       </c>
       <c r="M7" t="n">
-        <v>3.844214604871371</v>
+        <v>3.836945476686862</v>
       </c>
       <c r="N7" t="n">
-        <v>26.36473351668164</v>
+        <v>26.26162809931144</v>
       </c>
       <c r="O7" t="n">
-        <v>5.134660019580814</v>
+        <v>5.124610043633705</v>
       </c>
       <c r="P7" t="n">
-        <v>344.5714336565487</v>
+        <v>344.5605661641801</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27108,28 +27255,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3139451012499661</v>
+        <v>-0.3136828143309218</v>
       </c>
       <c r="J8" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="K8" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1796451702528223</v>
+        <v>0.1809433940662201</v>
       </c>
       <c r="M8" t="n">
-        <v>3.609407018930656</v>
+        <v>3.604422964278857</v>
       </c>
       <c r="N8" t="n">
-        <v>23.9440224911018</v>
+        <v>23.85523366971536</v>
       </c>
       <c r="O8" t="n">
-        <v>4.893262969747467</v>
+        <v>4.884181985728557</v>
       </c>
       <c r="P8" t="n">
-        <v>339.4520821999751</v>
+        <v>339.4491703316079</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27186,28 +27333,28 @@
         <v>0.0692</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2604874053181223</v>
+        <v>-0.2601483999802829</v>
       </c>
       <c r="J9" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="K9" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1259000735635919</v>
+        <v>0.1268121905323211</v>
       </c>
       <c r="M9" t="n">
-        <v>4.035718605496619</v>
+        <v>4.02632855321763</v>
       </c>
       <c r="N9" t="n">
-        <v>25.06178823924316</v>
+        <v>24.95858823441497</v>
       </c>
       <c r="O9" t="n">
-        <v>5.006175010848418</v>
+        <v>4.995857107085326</v>
       </c>
       <c r="P9" t="n">
-        <v>332.3650896046479</v>
+        <v>332.361316147968</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27264,28 +27411,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3140014115811269</v>
+        <v>-0.3138682194691406</v>
       </c>
       <c r="J10" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="K10" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1265592125453767</v>
+        <v>0.1278047977392593</v>
       </c>
       <c r="M10" t="n">
-        <v>5.005227473888966</v>
+        <v>4.984864650479568</v>
       </c>
       <c r="N10" t="n">
-        <v>36.19981924746612</v>
+        <v>36.00744134481112</v>
       </c>
       <c r="O10" t="n">
-        <v>6.016628561533953</v>
+        <v>6.00062008002599</v>
       </c>
       <c r="P10" t="n">
-        <v>331.3404597118676</v>
+        <v>331.3389835325713</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27323,7 +27470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K519"/>
+  <dimension ref="A1:K522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56905,6 +57052,177 @@
         </is>
       </c>
     </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>-46.61338401051096,168.83171667243704</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>-46.612796397035076,168.83200767515623</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>-46.61216942710444,168.8322204699443</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>-46.61154518247858,168.83227858046695</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>-46.610925574811894,168.83223112940948</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>-46.610309385287806,168.8320702065676</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>-46.609729816848905,168.83180066840035</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>-46.60914923773043,168.83149052709828</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>-46.60857558863057,168.83116015052948</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>-46.6133879988128,168.83172894071922</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>-46.61279888970988,168.8320153427606</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>-46.612171562731206,168.83223246691895</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>-46.61154564566222,168.83230022105664</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>-46.61092557186023,168.8323122546105</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>-46.61030170783288,168.83214370925788</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>-46.609712127888024,168.83187057697552</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>-46.609130863107985,168.8315535942553</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>-46.60856571889108,168.83119402627406</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>-46.61339279244314,168.83174368625316</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>-46.61280594589429,168.83203704798308</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>-46.612173968119876,168.83224597930217</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>-46.61154592747674,168.83231338792177</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>-46.61092557151963,168.83232151488292</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>-46.61030112865451,168.83214925419696</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>-46.60970946369745,168.83188110610922</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>-46.60912834315694,168.83156224346223</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>-46.608561658995185,168.8312079609741</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
